--- a/docs/payment-schedule-templates/Payment Schedules - Customer Portal/Collection_Schedule_Template_48mo.xlsx
+++ b/docs/payment-schedule-templates/Payment Schedules - Customer Portal/Collection_Schedule_Template_48mo.xlsx
@@ -1127,20 +1127,55 @@
       </c>
     </row>
     <row r="2" ht="15" customHeight="1" s="14">
-      <c r="A2" s="20" t="n"/>
-      <c r="B2" s="20" t="n"/>
-      <c r="C2" s="20" t="n"/>
-      <c r="D2" s="20" t="n"/>
-      <c r="E2" s="20" t="n"/>
-      <c r="F2" s="20" t="n"/>
-      <c r="G2" s="21" t="n"/>
-      <c r="H2" s="21" t="n"/>
-      <c r="I2" s="21" t="n"/>
+      <c r="A2" s="20" t="inlineStr">
+        <is>
+          <t>{{########}}</t>
+        </is>
+      </c>
+      <c r="B2" s="20" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C2" s="20" t="inlineStr">
+        <is>
+          <t>Nyandoro</t>
+        </is>
+      </c>
+      <c r="D2" s="20" t="inlineStr">
+        <is>
+          <t>+17785808657</t>
+        </is>
+      </c>
+      <c r="E2" s="20" t="inlineStr">
+        <is>
+          <t>alex@michaeltenable.com</t>
+        </is>
+      </c>
+      <c r="F2" s="20" t="inlineStr">
+        <is>
+          <t>Internal Tester</t>
+        </is>
+      </c>
+      <c r="G2" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="21" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I2" s="21" t="n">
+        <v>120000</v>
+      </c>
       <c r="J2" s="22" t="n">
         <v>48</v>
       </c>
-      <c r="K2" s="21" t="n"/>
-      <c r="L2" s="23" t="n"/>
+      <c r="K2" s="21">
+        <f>IF(J2=0,"",ROUND((I2-H2)/J2,2))</f>
+        <v/>
+      </c>
+      <c r="L2" s="23" t="n">
+        <v>46147</v>
+      </c>
       <c r="M2" s="21" t="n"/>
       <c r="N2" s="21" t="n"/>
       <c r="O2" s="21" t="n"/>
@@ -1191,15 +1226,15 @@
       <c r="BH2" s="21" t="n"/>
       <c r="BI2" s="21" t="n"/>
       <c r="BJ2" s="24">
-        <f>SUM(M2:BH2)</f>
+        <f>H2+SUM(M2:BH2)</f>
         <v/>
       </c>
       <c r="BK2" s="24">
-        <f>I2-BJ2</f>
+        <f>I2-H2-SUM(M2:BH2)</f>
         <v/>
       </c>
       <c r="BL2" s="25">
-        <f>IF(I2=0,"",BJ2/I2)</f>
+        <f>IF(I2=0,"",(H2+SUM(M2:BH2))/I2)</f>
         <v/>
       </c>
       <c r="BM2" s="26" t="n"/>
@@ -1276,15 +1311,15 @@
       <c r="BH3" s="21" t="n"/>
       <c r="BI3" s="21" t="n"/>
       <c r="BJ3" s="24">
-        <f>SUM(M3:BH3)</f>
+        <f>H3+SUM(M3:BH3)</f>
         <v/>
       </c>
       <c r="BK3" s="24">
-        <f>I3-BJ3</f>
+        <f>I3-H3-SUM(M3:BH3)</f>
         <v/>
       </c>
       <c r="BL3" s="25">
-        <f>IF(I3=0,"",BJ3/I3)</f>
+        <f>IF(I3=0,"",(H3+SUM(M3:BH3))/I3)</f>
         <v/>
       </c>
       <c r="BM3" s="26" t="n"/>
@@ -1361,15 +1396,15 @@
       <c r="BH4" s="21" t="n"/>
       <c r="BI4" s="21" t="n"/>
       <c r="BJ4" s="24">
-        <f>SUM(M4:BH4)</f>
+        <f>H4+SUM(M4:BH4)</f>
         <v/>
       </c>
       <c r="BK4" s="24">
-        <f>I4-BJ4</f>
+        <f>I4-H4-SUM(M4:BH4)</f>
         <v/>
       </c>
       <c r="BL4" s="25">
-        <f>IF(I4=0,"",BJ4/I4)</f>
+        <f>IF(I4=0,"",(H4+SUM(M4:BH4))/I4)</f>
         <v/>
       </c>
       <c r="BM4" s="26" t="n"/>
@@ -1446,15 +1481,15 @@
       <c r="BH5" s="21" t="n"/>
       <c r="BI5" s="21" t="n"/>
       <c r="BJ5" s="24">
-        <f>SUM(M5:BH5)</f>
+        <f>H5+SUM(M5:BH5)</f>
         <v/>
       </c>
       <c r="BK5" s="24">
-        <f>I5-BJ5</f>
+        <f>I5-H5-SUM(M5:BH5)</f>
         <v/>
       </c>
       <c r="BL5" s="25">
-        <f>IF(I5=0,"",BJ5/I5)</f>
+        <f>IF(I5=0,"",(H5+SUM(M5:BH5))/I5)</f>
         <v/>
       </c>
       <c r="BM5" s="26" t="n"/>
@@ -1531,15 +1566,15 @@
       <c r="BH6" s="21" t="n"/>
       <c r="BI6" s="21" t="n"/>
       <c r="BJ6" s="24">
-        <f>SUM(M6:BH6)</f>
+        <f>H6+SUM(M6:BH6)</f>
         <v/>
       </c>
       <c r="BK6" s="24">
-        <f>I6-BJ6</f>
+        <f>I6-H6-SUM(M6:BH6)</f>
         <v/>
       </c>
       <c r="BL6" s="25">
-        <f>IF(I6=0,"",BJ6/I6)</f>
+        <f>IF(I6=0,"",(H6+SUM(M6:BH6))/I6)</f>
         <v/>
       </c>
       <c r="BM6" s="26" t="n"/>
@@ -1616,15 +1651,15 @@
       <c r="BH7" s="21" t="n"/>
       <c r="BI7" s="21" t="n"/>
       <c r="BJ7" s="24">
-        <f>SUM(M7:BH7)</f>
+        <f>H7+SUM(M7:BH7)</f>
         <v/>
       </c>
       <c r="BK7" s="24">
-        <f>I7-BJ7</f>
+        <f>I7-H7-SUM(M7:BH7)</f>
         <v/>
       </c>
       <c r="BL7" s="25">
-        <f>IF(I7=0,"",BJ7/I7)</f>
+        <f>IF(I7=0,"",(H7+SUM(M7:BH7))/I7)</f>
         <v/>
       </c>
       <c r="BM7" s="26" t="n"/>
@@ -1701,15 +1736,15 @@
       <c r="BH8" s="21" t="n"/>
       <c r="BI8" s="21" t="n"/>
       <c r="BJ8" s="24">
-        <f>SUM(M8:BH8)</f>
+        <f>H8+SUM(M8:BH8)</f>
         <v/>
       </c>
       <c r="BK8" s="24">
-        <f>I8-BJ8</f>
+        <f>I8-H8-SUM(M8:BH8)</f>
         <v/>
       </c>
       <c r="BL8" s="25">
-        <f>IF(I8=0,"",BJ8/I8)</f>
+        <f>IF(I8=0,"",(H8+SUM(M8:BH8))/I8)</f>
         <v/>
       </c>
       <c r="BM8" s="26" t="n"/>
@@ -1786,15 +1821,15 @@
       <c r="BH9" s="21" t="n"/>
       <c r="BI9" s="21" t="n"/>
       <c r="BJ9" s="24">
-        <f>SUM(M9:BH9)</f>
+        <f>H9+SUM(M9:BH9)</f>
         <v/>
       </c>
       <c r="BK9" s="24">
-        <f>I9-BJ9</f>
+        <f>I9-H9-SUM(M9:BH9)</f>
         <v/>
       </c>
       <c r="BL9" s="25">
-        <f>IF(I9=0,"",BJ9/I9)</f>
+        <f>IF(I9=0,"",(H9+SUM(M9:BH9))/I9)</f>
         <v/>
       </c>
       <c r="BM9" s="26" t="n"/>
@@ -1871,15 +1906,15 @@
       <c r="BH10" s="21" t="n"/>
       <c r="BI10" s="21" t="n"/>
       <c r="BJ10" s="24">
-        <f>SUM(M10:BH10)</f>
+        <f>H10+SUM(M10:BH10)</f>
         <v/>
       </c>
       <c r="BK10" s="24">
-        <f>I10-BJ10</f>
+        <f>I10-H10-SUM(M10:BH10)</f>
         <v/>
       </c>
       <c r="BL10" s="25">
-        <f>IF(I10=0,"",BJ10/I10)</f>
+        <f>IF(I10=0,"",(H10+SUM(M10:BH10))/I10)</f>
         <v/>
       </c>
       <c r="BM10" s="26" t="n"/>
@@ -1956,15 +1991,15 @@
       <c r="BH11" s="21" t="n"/>
       <c r="BI11" s="21" t="n"/>
       <c r="BJ11" s="24">
-        <f>SUM(M11:BH11)</f>
+        <f>H11+SUM(M11:BH11)</f>
         <v/>
       </c>
       <c r="BK11" s="24">
-        <f>I11-BJ11</f>
+        <f>I11-H11-SUM(M11:BH11)</f>
         <v/>
       </c>
       <c r="BL11" s="25">
-        <f>IF(I11=0,"",BJ11/I11)</f>
+        <f>IF(I11=0,"",(H11+SUM(M11:BH11))/I11)</f>
         <v/>
       </c>
       <c r="BM11" s="26" t="n"/>
@@ -2041,15 +2076,15 @@
       <c r="BH12" s="21" t="n"/>
       <c r="BI12" s="21" t="n"/>
       <c r="BJ12" s="24">
-        <f>SUM(M12:BH12)</f>
+        <f>H12+SUM(M12:BH12)</f>
         <v/>
       </c>
       <c r="BK12" s="24">
-        <f>I12-BJ12</f>
+        <f>I12-H12-SUM(M12:BH12)</f>
         <v/>
       </c>
       <c r="BL12" s="25">
-        <f>IF(I12=0,"",BJ12/I12)</f>
+        <f>IF(I12=0,"",(H12+SUM(M12:BH12))/I12)</f>
         <v/>
       </c>
       <c r="BM12" s="26" t="n"/>
@@ -2126,15 +2161,15 @@
       <c r="BH13" s="21" t="n"/>
       <c r="BI13" s="21" t="n"/>
       <c r="BJ13" s="24">
-        <f>SUM(M13:BH13)</f>
+        <f>H13+SUM(M13:BH13)</f>
         <v/>
       </c>
       <c r="BK13" s="24">
-        <f>I13-BJ13</f>
+        <f>I13-H13-SUM(M13:BH13)</f>
         <v/>
       </c>
       <c r="BL13" s="25">
-        <f>IF(I13=0,"",BJ13/I13)</f>
+        <f>IF(I13=0,"",(H13+SUM(M13:BH13))/I13)</f>
         <v/>
       </c>
       <c r="BM13" s="26" t="n"/>
@@ -2211,15 +2246,15 @@
       <c r="BH14" s="21" t="n"/>
       <c r="BI14" s="21" t="n"/>
       <c r="BJ14" s="24">
-        <f>SUM(M14:BH14)</f>
+        <f>H14+SUM(M14:BH14)</f>
         <v/>
       </c>
       <c r="BK14" s="24">
-        <f>I14-BJ14</f>
+        <f>I14-H14-SUM(M14:BH14)</f>
         <v/>
       </c>
       <c r="BL14" s="25">
-        <f>IF(I14=0,"",BJ14/I14)</f>
+        <f>IF(I14=0,"",(H14+SUM(M14:BH14))/I14)</f>
         <v/>
       </c>
       <c r="BM14" s="26" t="n"/>
@@ -2296,15 +2331,15 @@
       <c r="BH15" s="21" t="n"/>
       <c r="BI15" s="21" t="n"/>
       <c r="BJ15" s="24">
-        <f>SUM(M15:BH15)</f>
+        <f>H15+SUM(M15:BH15)</f>
         <v/>
       </c>
       <c r="BK15" s="24">
-        <f>I15-BJ15</f>
+        <f>I15-H15-SUM(M15:BH15)</f>
         <v/>
       </c>
       <c r="BL15" s="25">
-        <f>IF(I15=0,"",BJ15/I15)</f>
+        <f>IF(I15=0,"",(H15+SUM(M15:BH15))/I15)</f>
         <v/>
       </c>
       <c r="BM15" s="26" t="n"/>
@@ -2381,15 +2416,15 @@
       <c r="BH16" s="21" t="n"/>
       <c r="BI16" s="21" t="n"/>
       <c r="BJ16" s="24">
-        <f>SUM(M16:BH16)</f>
+        <f>H16+SUM(M16:BH16)</f>
         <v/>
       </c>
       <c r="BK16" s="24">
-        <f>I16-BJ16</f>
+        <f>I16-H16-SUM(M16:BH16)</f>
         <v/>
       </c>
       <c r="BL16" s="25">
-        <f>IF(I16=0,"",BJ16/I16)</f>
+        <f>IF(I16=0,"",(H16+SUM(M16:BH16))/I16)</f>
         <v/>
       </c>
       <c r="BM16" s="26" t="n"/>
@@ -2466,15 +2501,15 @@
       <c r="BH17" s="21" t="n"/>
       <c r="BI17" s="21" t="n"/>
       <c r="BJ17" s="24">
-        <f>SUM(M17:BH17)</f>
+        <f>H17+SUM(M17:BH17)</f>
         <v/>
       </c>
       <c r="BK17" s="24">
-        <f>I17-BJ17</f>
+        <f>I17-H17-SUM(M17:BH17)</f>
         <v/>
       </c>
       <c r="BL17" s="25">
-        <f>IF(I17=0,"",BJ17/I17)</f>
+        <f>IF(I17=0,"",(H17+SUM(M17:BH17))/I17)</f>
         <v/>
       </c>
       <c r="BM17" s="26" t="n"/>
@@ -2551,15 +2586,15 @@
       <c r="BH18" s="21" t="n"/>
       <c r="BI18" s="21" t="n"/>
       <c r="BJ18" s="24">
-        <f>SUM(M18:BH18)</f>
+        <f>H18+SUM(M18:BH18)</f>
         <v/>
       </c>
       <c r="BK18" s="24">
-        <f>I18-BJ18</f>
+        <f>I18-H18-SUM(M18:BH18)</f>
         <v/>
       </c>
       <c r="BL18" s="25">
-        <f>IF(I18=0,"",BJ18/I18)</f>
+        <f>IF(I18=0,"",(H18+SUM(M18:BH18))/I18)</f>
         <v/>
       </c>
       <c r="BM18" s="26" t="n"/>
@@ -2636,15 +2671,15 @@
       <c r="BH19" s="21" t="n"/>
       <c r="BI19" s="21" t="n"/>
       <c r="BJ19" s="24">
-        <f>SUM(M19:BH19)</f>
+        <f>H19+SUM(M19:BH19)</f>
         <v/>
       </c>
       <c r="BK19" s="24">
-        <f>I19-BJ19</f>
+        <f>I19-H19-SUM(M19:BH19)</f>
         <v/>
       </c>
       <c r="BL19" s="25">
-        <f>IF(I19=0,"",BJ19/I19)</f>
+        <f>IF(I19=0,"",(H19+SUM(M19:BH19))/I19)</f>
         <v/>
       </c>
       <c r="BM19" s="26" t="n"/>
@@ -2721,15 +2756,15 @@
       <c r="BH20" s="21" t="n"/>
       <c r="BI20" s="21" t="n"/>
       <c r="BJ20" s="24">
-        <f>SUM(M20:BH20)</f>
+        <f>H20+SUM(M20:BH20)</f>
         <v/>
       </c>
       <c r="BK20" s="24">
-        <f>I20-BJ20</f>
+        <f>I20-H20-SUM(M20:BH20)</f>
         <v/>
       </c>
       <c r="BL20" s="25">
-        <f>IF(I20=0,"",BJ20/I20)</f>
+        <f>IF(I20=0,"",(H20+SUM(M20:BH20))/I20)</f>
         <v/>
       </c>
       <c r="BM20" s="26" t="n"/>
@@ -2806,15 +2841,15 @@
       <c r="BH21" s="21" t="n"/>
       <c r="BI21" s="21" t="n"/>
       <c r="BJ21" s="24">
-        <f>SUM(M21:BH21)</f>
+        <f>H21+SUM(M21:BH21)</f>
         <v/>
       </c>
       <c r="BK21" s="24">
-        <f>I21-BJ21</f>
+        <f>I21-H21-SUM(M21:BH21)</f>
         <v/>
       </c>
       <c r="BL21" s="25">
-        <f>IF(I21=0,"",BJ21/I21)</f>
+        <f>IF(I21=0,"",(H21+SUM(M21:BH21))/I21)</f>
         <v/>
       </c>
       <c r="BM21" s="26" t="n"/>
@@ -2891,15 +2926,15 @@
       <c r="BH22" s="21" t="n"/>
       <c r="BI22" s="21" t="n"/>
       <c r="BJ22" s="24">
-        <f>SUM(M22:BH22)</f>
+        <f>H22+SUM(M22:BH22)</f>
         <v/>
       </c>
       <c r="BK22" s="24">
-        <f>I22-BJ22</f>
+        <f>I22-H22-SUM(M22:BH22)</f>
         <v/>
       </c>
       <c r="BL22" s="25">
-        <f>IF(I22=0,"",BJ22/I22)</f>
+        <f>IF(I22=0,"",(H22+SUM(M22:BH22))/I22)</f>
         <v/>
       </c>
       <c r="BM22" s="26" t="n"/>
@@ -2976,15 +3011,15 @@
       <c r="BH23" s="21" t="n"/>
       <c r="BI23" s="21" t="n"/>
       <c r="BJ23" s="24">
-        <f>SUM(M23:BH23)</f>
+        <f>H23+SUM(M23:BH23)</f>
         <v/>
       </c>
       <c r="BK23" s="24">
-        <f>I23-BJ23</f>
+        <f>I23-H23-SUM(M23:BH23)</f>
         <v/>
       </c>
       <c r="BL23" s="25">
-        <f>IF(I23=0,"",BJ23/I23)</f>
+        <f>IF(I23=0,"",(H23+SUM(M23:BH23))/I23)</f>
         <v/>
       </c>
       <c r="BM23" s="26" t="n"/>
@@ -3061,15 +3096,15 @@
       <c r="BH24" s="21" t="n"/>
       <c r="BI24" s="21" t="n"/>
       <c r="BJ24" s="24">
-        <f>SUM(M24:BH24)</f>
+        <f>H24+SUM(M24:BH24)</f>
         <v/>
       </c>
       <c r="BK24" s="24">
-        <f>I24-BJ24</f>
+        <f>I24-H24-SUM(M24:BH24)</f>
         <v/>
       </c>
       <c r="BL24" s="25">
-        <f>IF(I24=0,"",BJ24/I24)</f>
+        <f>IF(I24=0,"",(H24+SUM(M24:BH24))/I24)</f>
         <v/>
       </c>
       <c r="BM24" s="26" t="n"/>
@@ -3146,15 +3181,15 @@
       <c r="BH25" s="21" t="n"/>
       <c r="BI25" s="21" t="n"/>
       <c r="BJ25" s="24">
-        <f>SUM(M25:BH25)</f>
+        <f>H25+SUM(M25:BH25)</f>
         <v/>
       </c>
       <c r="BK25" s="24">
-        <f>I25-BJ25</f>
+        <f>I25-H25-SUM(M25:BH25)</f>
         <v/>
       </c>
       <c r="BL25" s="25">
-        <f>IF(I25=0,"",BJ25/I25)</f>
+        <f>IF(I25=0,"",(H25+SUM(M25:BH25))/I25)</f>
         <v/>
       </c>
       <c r="BM25" s="26" t="n"/>
@@ -3231,15 +3266,15 @@
       <c r="BH26" s="21" t="n"/>
       <c r="BI26" s="21" t="n"/>
       <c r="BJ26" s="24">
-        <f>SUM(M26:BH26)</f>
+        <f>H26+SUM(M26:BH26)</f>
         <v/>
       </c>
       <c r="BK26" s="24">
-        <f>I26-BJ26</f>
+        <f>I26-H26-SUM(M26:BH26)</f>
         <v/>
       </c>
       <c r="BL26" s="25">
-        <f>IF(I26=0,"",BJ26/I26)</f>
+        <f>IF(I26=0,"",(H26+SUM(M26:BH26))/I26)</f>
         <v/>
       </c>
       <c r="BM26" s="26" t="n"/>
@@ -3316,15 +3351,15 @@
       <c r="BH27" s="21" t="n"/>
       <c r="BI27" s="21" t="n"/>
       <c r="BJ27" s="24">
-        <f>SUM(M27:BH27)</f>
+        <f>H27+SUM(M27:BH27)</f>
         <v/>
       </c>
       <c r="BK27" s="24">
-        <f>I27-BJ27</f>
+        <f>I27-H27-SUM(M27:BH27)</f>
         <v/>
       </c>
       <c r="BL27" s="25">
-        <f>IF(I27=0,"",BJ27/I27)</f>
+        <f>IF(I27=0,"",(H27+SUM(M27:BH27))/I27)</f>
         <v/>
       </c>
       <c r="BM27" s="26" t="n"/>
@@ -3401,15 +3436,15 @@
       <c r="BH28" s="21" t="n"/>
       <c r="BI28" s="21" t="n"/>
       <c r="BJ28" s="24">
-        <f>SUM(M28:BH28)</f>
+        <f>H28+SUM(M28:BH28)</f>
         <v/>
       </c>
       <c r="BK28" s="24">
-        <f>I28-BJ28</f>
+        <f>I28-H28-SUM(M28:BH28)</f>
         <v/>
       </c>
       <c r="BL28" s="25">
-        <f>IF(I28=0,"",BJ28/I28)</f>
+        <f>IF(I28=0,"",(H28+SUM(M28:BH28))/I28)</f>
         <v/>
       </c>
       <c r="BM28" s="26" t="n"/>
@@ -3486,15 +3521,15 @@
       <c r="BH29" s="21" t="n"/>
       <c r="BI29" s="21" t="n"/>
       <c r="BJ29" s="24">
-        <f>SUM(M29:BH29)</f>
+        <f>H29+SUM(M29:BH29)</f>
         <v/>
       </c>
       <c r="BK29" s="24">
-        <f>I29-BJ29</f>
+        <f>I29-H29-SUM(M29:BH29)</f>
         <v/>
       </c>
       <c r="BL29" s="25">
-        <f>IF(I29=0,"",BJ29/I29)</f>
+        <f>IF(I29=0,"",(H29+SUM(M29:BH29))/I29)</f>
         <v/>
       </c>
       <c r="BM29" s="26" t="n"/>
@@ -3571,15 +3606,15 @@
       <c r="BH30" s="21" t="n"/>
       <c r="BI30" s="21" t="n"/>
       <c r="BJ30" s="24">
-        <f>SUM(M30:BH30)</f>
+        <f>H30+SUM(M30:BH30)</f>
         <v/>
       </c>
       <c r="BK30" s="24">
-        <f>I30-BJ30</f>
+        <f>I30-H30-SUM(M30:BH30)</f>
         <v/>
       </c>
       <c r="BL30" s="25">
-        <f>IF(I30=0,"",BJ30/I30)</f>
+        <f>IF(I30=0,"",(H30+SUM(M30:BH30))/I30)</f>
         <v/>
       </c>
       <c r="BM30" s="26" t="n"/>
@@ -3656,15 +3691,15 @@
       <c r="BH31" s="21" t="n"/>
       <c r="BI31" s="21" t="n"/>
       <c r="BJ31" s="24">
-        <f>SUM(M31:BH31)</f>
+        <f>H31+SUM(M31:BH31)</f>
         <v/>
       </c>
       <c r="BK31" s="24">
-        <f>I31-BJ31</f>
+        <f>I31-H31-SUM(M31:BH31)</f>
         <v/>
       </c>
       <c r="BL31" s="25">
-        <f>IF(I31=0,"",BJ31/I31)</f>
+        <f>IF(I31=0,"",(H31+SUM(M31:BH31))/I31)</f>
         <v/>
       </c>
       <c r="BM31" s="26" t="n"/>
@@ -3741,15 +3776,15 @@
       <c r="BH32" s="21" t="n"/>
       <c r="BI32" s="21" t="n"/>
       <c r="BJ32" s="24">
-        <f>SUM(M32:BH32)</f>
+        <f>H32+SUM(M32:BH32)</f>
         <v/>
       </c>
       <c r="BK32" s="24">
-        <f>I32-BJ32</f>
+        <f>I32-H32-SUM(M32:BH32)</f>
         <v/>
       </c>
       <c r="BL32" s="25">
-        <f>IF(I32=0,"",BJ32/I32)</f>
+        <f>IF(I32=0,"",(H32+SUM(M32:BH32))/I32)</f>
         <v/>
       </c>
       <c r="BM32" s="26" t="n"/>
@@ -3826,15 +3861,15 @@
       <c r="BH33" s="21" t="n"/>
       <c r="BI33" s="21" t="n"/>
       <c r="BJ33" s="24">
-        <f>SUM(M33:BH33)</f>
+        <f>H33+SUM(M33:BH33)</f>
         <v/>
       </c>
       <c r="BK33" s="24">
-        <f>I33-BJ33</f>
+        <f>I33-H33-SUM(M33:BH33)</f>
         <v/>
       </c>
       <c r="BL33" s="25">
-        <f>IF(I33=0,"",BJ33/I33)</f>
+        <f>IF(I33=0,"",(H33+SUM(M33:BH33))/I33)</f>
         <v/>
       </c>
       <c r="BM33" s="26" t="n"/>
@@ -3911,15 +3946,15 @@
       <c r="BH34" s="21" t="n"/>
       <c r="BI34" s="21" t="n"/>
       <c r="BJ34" s="24">
-        <f>SUM(M34:BH34)</f>
+        <f>H34+SUM(M34:BH34)</f>
         <v/>
       </c>
       <c r="BK34" s="24">
-        <f>I34-BJ34</f>
+        <f>I34-H34-SUM(M34:BH34)</f>
         <v/>
       </c>
       <c r="BL34" s="25">
-        <f>IF(I34=0,"",BJ34/I34)</f>
+        <f>IF(I34=0,"",(H34+SUM(M34:BH34))/I34)</f>
         <v/>
       </c>
       <c r="BM34" s="26" t="n"/>
@@ -3996,15 +4031,15 @@
       <c r="BH35" s="21" t="n"/>
       <c r="BI35" s="21" t="n"/>
       <c r="BJ35" s="24">
-        <f>SUM(M35:BH35)</f>
+        <f>H35+SUM(M35:BH35)</f>
         <v/>
       </c>
       <c r="BK35" s="24">
-        <f>I35-BJ35</f>
+        <f>I35-H35-SUM(M35:BH35)</f>
         <v/>
       </c>
       <c r="BL35" s="25">
-        <f>IF(I35=0,"",BJ35/I35)</f>
+        <f>IF(I35=0,"",(H35+SUM(M35:BH35))/I35)</f>
         <v/>
       </c>
       <c r="BM35" s="26" t="n"/>
@@ -4081,15 +4116,15 @@
       <c r="BH36" s="21" t="n"/>
       <c r="BI36" s="21" t="n"/>
       <c r="BJ36" s="24">
-        <f>SUM(M36:BH36)</f>
+        <f>H36+SUM(M36:BH36)</f>
         <v/>
       </c>
       <c r="BK36" s="24">
-        <f>I36-BJ36</f>
+        <f>I36-H36-SUM(M36:BH36)</f>
         <v/>
       </c>
       <c r="BL36" s="25">
-        <f>IF(I36=0,"",BJ36/I36)</f>
+        <f>IF(I36=0,"",(H36+SUM(M36:BH36))/I36)</f>
         <v/>
       </c>
       <c r="BM36" s="26" t="n"/>
@@ -4166,15 +4201,15 @@
       <c r="BH37" s="21" t="n"/>
       <c r="BI37" s="21" t="n"/>
       <c r="BJ37" s="24">
-        <f>SUM(M37:BH37)</f>
+        <f>H37+SUM(M37:BH37)</f>
         <v/>
       </c>
       <c r="BK37" s="24">
-        <f>I37-BJ37</f>
+        <f>I37-H37-SUM(M37:BH37)</f>
         <v/>
       </c>
       <c r="BL37" s="25">
-        <f>IF(I37=0,"",BJ37/I37)</f>
+        <f>IF(I37=0,"",(H37+SUM(M37:BH37))/I37)</f>
         <v/>
       </c>
       <c r="BM37" s="26" t="n"/>
@@ -4251,15 +4286,15 @@
       <c r="BH38" s="21" t="n"/>
       <c r="BI38" s="21" t="n"/>
       <c r="BJ38" s="24">
-        <f>SUM(M38:BH38)</f>
+        <f>H38+SUM(M38:BH38)</f>
         <v/>
       </c>
       <c r="BK38" s="24">
-        <f>I38-BJ38</f>
+        <f>I38-H38-SUM(M38:BH38)</f>
         <v/>
       </c>
       <c r="BL38" s="25">
-        <f>IF(I38=0,"",BJ38/I38)</f>
+        <f>IF(I38=0,"",(H38+SUM(M38:BH38))/I38)</f>
         <v/>
       </c>
       <c r="BM38" s="26" t="n"/>
@@ -4336,15 +4371,15 @@
       <c r="BH39" s="21" t="n"/>
       <c r="BI39" s="21" t="n"/>
       <c r="BJ39" s="24">
-        <f>SUM(M39:BH39)</f>
+        <f>H39+SUM(M39:BH39)</f>
         <v/>
       </c>
       <c r="BK39" s="24">
-        <f>I39-BJ39</f>
+        <f>I39-H39-SUM(M39:BH39)</f>
         <v/>
       </c>
       <c r="BL39" s="25">
-        <f>IF(I39=0,"",BJ39/I39)</f>
+        <f>IF(I39=0,"",(H39+SUM(M39:BH39))/I39)</f>
         <v/>
       </c>
       <c r="BM39" s="26" t="n"/>
@@ -4421,15 +4456,15 @@
       <c r="BH40" s="21" t="n"/>
       <c r="BI40" s="21" t="n"/>
       <c r="BJ40" s="24">
-        <f>SUM(M40:BH40)</f>
+        <f>H40+SUM(M40:BH40)</f>
         <v/>
       </c>
       <c r="BK40" s="24">
-        <f>I40-BJ40</f>
+        <f>I40-H40-SUM(M40:BH40)</f>
         <v/>
       </c>
       <c r="BL40" s="25">
-        <f>IF(I40=0,"",BJ40/I40)</f>
+        <f>IF(I40=0,"",(H40+SUM(M40:BH40))/I40)</f>
         <v/>
       </c>
       <c r="BM40" s="26" t="n"/>
@@ -4506,15 +4541,15 @@
       <c r="BH41" s="21" t="n"/>
       <c r="BI41" s="21" t="n"/>
       <c r="BJ41" s="24">
-        <f>SUM(M41:BH41)</f>
+        <f>H41+SUM(M41:BH41)</f>
         <v/>
       </c>
       <c r="BK41" s="24">
-        <f>I41-BJ41</f>
+        <f>I41-H41-SUM(M41:BH41)</f>
         <v/>
       </c>
       <c r="BL41" s="25">
-        <f>IF(I41=0,"",BJ41/I41)</f>
+        <f>IF(I41=0,"",(H41+SUM(M41:BH41))/I41)</f>
         <v/>
       </c>
       <c r="BM41" s="26" t="n"/>
@@ -4591,15 +4626,15 @@
       <c r="BH42" s="21" t="n"/>
       <c r="BI42" s="21" t="n"/>
       <c r="BJ42" s="24">
-        <f>SUM(M42:BH42)</f>
+        <f>H42+SUM(M42:BH42)</f>
         <v/>
       </c>
       <c r="BK42" s="24">
-        <f>I42-BJ42</f>
+        <f>I42-H42-SUM(M42:BH42)</f>
         <v/>
       </c>
       <c r="BL42" s="25">
-        <f>IF(I42=0,"",BJ42/I42)</f>
+        <f>IF(I42=0,"",(H42+SUM(M42:BH42))/I42)</f>
         <v/>
       </c>
       <c r="BM42" s="26" t="n"/>
@@ -4676,15 +4711,15 @@
       <c r="BH43" s="21" t="n"/>
       <c r="BI43" s="21" t="n"/>
       <c r="BJ43" s="24">
-        <f>SUM(M43:BH43)</f>
+        <f>H43+SUM(M43:BH43)</f>
         <v/>
       </c>
       <c r="BK43" s="24">
-        <f>I43-BJ43</f>
+        <f>I43-H43-SUM(M43:BH43)</f>
         <v/>
       </c>
       <c r="BL43" s="25">
-        <f>IF(I43=0,"",BJ43/I43)</f>
+        <f>IF(I43=0,"",(H43+SUM(M43:BH43))/I43)</f>
         <v/>
       </c>
       <c r="BM43" s="26" t="n"/>
@@ -4761,15 +4796,15 @@
       <c r="BH44" s="21" t="n"/>
       <c r="BI44" s="21" t="n"/>
       <c r="BJ44" s="24">
-        <f>SUM(M44:BH44)</f>
+        <f>H44+SUM(M44:BH44)</f>
         <v/>
       </c>
       <c r="BK44" s="24">
-        <f>I44-BJ44</f>
+        <f>I44-H44-SUM(M44:BH44)</f>
         <v/>
       </c>
       <c r="BL44" s="25">
-        <f>IF(I44=0,"",BJ44/I44)</f>
+        <f>IF(I44=0,"",(H44+SUM(M44:BH44))/I44)</f>
         <v/>
       </c>
       <c r="BM44" s="26" t="n"/>
@@ -4846,15 +4881,15 @@
       <c r="BH45" s="21" t="n"/>
       <c r="BI45" s="21" t="n"/>
       <c r="BJ45" s="24">
-        <f>SUM(M45:BH45)</f>
+        <f>H45+SUM(M45:BH45)</f>
         <v/>
       </c>
       <c r="BK45" s="24">
-        <f>I45-BJ45</f>
+        <f>I45-H45-SUM(M45:BH45)</f>
         <v/>
       </c>
       <c r="BL45" s="25">
-        <f>IF(I45=0,"",BJ45/I45)</f>
+        <f>IF(I45=0,"",(H45+SUM(M45:BH45))/I45)</f>
         <v/>
       </c>
       <c r="BM45" s="26" t="n"/>
@@ -4931,15 +4966,15 @@
       <c r="BH46" s="21" t="n"/>
       <c r="BI46" s="21" t="n"/>
       <c r="BJ46" s="24">
-        <f>SUM(M46:BH46)</f>
+        <f>H46+SUM(M46:BH46)</f>
         <v/>
       </c>
       <c r="BK46" s="24">
-        <f>I46-BJ46</f>
+        <f>I46-H46-SUM(M46:BH46)</f>
         <v/>
       </c>
       <c r="BL46" s="25">
-        <f>IF(I46=0,"",BJ46/I46)</f>
+        <f>IF(I46=0,"",(H46+SUM(M46:BH46))/I46)</f>
         <v/>
       </c>
       <c r="BM46" s="26" t="n"/>
@@ -5016,15 +5051,15 @@
       <c r="BH47" s="21" t="n"/>
       <c r="BI47" s="21" t="n"/>
       <c r="BJ47" s="24">
-        <f>SUM(M47:BH47)</f>
+        <f>H47+SUM(M47:BH47)</f>
         <v/>
       </c>
       <c r="BK47" s="24">
-        <f>I47-BJ47</f>
+        <f>I47-H47-SUM(M47:BH47)</f>
         <v/>
       </c>
       <c r="BL47" s="25">
-        <f>IF(I47=0,"",BJ47/I47)</f>
+        <f>IF(I47=0,"",(H47+SUM(M47:BH47))/I47)</f>
         <v/>
       </c>
       <c r="BM47" s="26" t="n"/>
@@ -5101,15 +5136,15 @@
       <c r="BH48" s="21" t="n"/>
       <c r="BI48" s="21" t="n"/>
       <c r="BJ48" s="24">
-        <f>SUM(M48:BH48)</f>
+        <f>H48+SUM(M48:BH48)</f>
         <v/>
       </c>
       <c r="BK48" s="24">
-        <f>I48-BJ48</f>
+        <f>I48-H48-SUM(M48:BH48)</f>
         <v/>
       </c>
       <c r="BL48" s="25">
-        <f>IF(I48=0,"",BJ48/I48)</f>
+        <f>IF(I48=0,"",(H48+SUM(M48:BH48))/I48)</f>
         <v/>
       </c>
       <c r="BM48" s="26" t="n"/>
@@ -5186,15 +5221,15 @@
       <c r="BH49" s="21" t="n"/>
       <c r="BI49" s="21" t="n"/>
       <c r="BJ49" s="24">
-        <f>SUM(M49:BH49)</f>
+        <f>H49+SUM(M49:BH49)</f>
         <v/>
       </c>
       <c r="BK49" s="24">
-        <f>I49-BJ49</f>
+        <f>I49-H49-SUM(M49:BH49)</f>
         <v/>
       </c>
       <c r="BL49" s="25">
-        <f>IF(I49=0,"",BJ49/I49)</f>
+        <f>IF(I49=0,"",(H49+SUM(M49:BH49))/I49)</f>
         <v/>
       </c>
       <c r="BM49" s="26" t="n"/>
@@ -5271,15 +5306,15 @@
       <c r="BH50" s="21" t="n"/>
       <c r="BI50" s="21" t="n"/>
       <c r="BJ50" s="24">
-        <f>SUM(M50:BH50)</f>
+        <f>H50+SUM(M50:BH50)</f>
         <v/>
       </c>
       <c r="BK50" s="24">
-        <f>I50-BJ50</f>
+        <f>I50-H50-SUM(M50:BH50)</f>
         <v/>
       </c>
       <c r="BL50" s="25">
-        <f>IF(I50=0,"",BJ50/I50)</f>
+        <f>IF(I50=0,"",(H50+SUM(M50:BH50))/I50)</f>
         <v/>
       </c>
       <c r="BM50" s="26" t="n"/>
@@ -5356,15 +5391,15 @@
       <c r="BH51" s="21" t="n"/>
       <c r="BI51" s="21" t="n"/>
       <c r="BJ51" s="24">
-        <f>SUM(M51:BH51)</f>
+        <f>H51+SUM(M51:BH51)</f>
         <v/>
       </c>
       <c r="BK51" s="24">
-        <f>I51-BJ51</f>
+        <f>I51-H51-SUM(M51:BH51)</f>
         <v/>
       </c>
       <c r="BL51" s="25">
-        <f>IF(I51=0,"",BJ51/I51)</f>
+        <f>IF(I51=0,"",(H51+SUM(M51:BH51))/I51)</f>
         <v/>
       </c>
       <c r="BM51" s="26" t="n"/>
